--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-23T09:47:34.071Z</t>
+    <t>2026-07-23T10:43:38.348Z</t>
   </si>
   <si>
     <t>Latest Luxury cars and experiences by Morris Garages In India | MG Select</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-23T10:43:38.348Z</t>
+    <t>2026-07-23T12:32:48.030Z</t>
   </si>
   <si>
     <t>Latest Luxury cars and experiences by Morris Garages In India | MG Select</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-23T12:32:48.030Z</t>
+    <t>2026-07-23T19:33:35.464Z</t>
   </si>
   <si>
     <t>Latest Luxury cars and experiences by Morris Garages In India | MG Select</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-23T19:33:35.464Z</t>
+    <t>2026-07-23T19:58:54.841Z</t>
   </si>
   <si>
     <t>Latest Luxury cars and experiences by Morris Garages In India | MG Select</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-23T19:58:54.841Z</t>
+    <t>2026-07-23T20:15:26.138Z</t>
   </si>
   <si>
     <t>Latest Luxury cars and experiences by Morris Garages In India | MG Select</t>
